--- a/results/q4_output/动态扩容方案.xlsx
+++ b/results/q4_output/动态扩容方案.xlsx
@@ -17,16 +17,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="1">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -37,7 +34,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -45,21 +42,12 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -425,366 +413,9 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J9"/>
+  <dimension ref="A1:A1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>情景</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>年份</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>区域</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>区域名称</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>健康度</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>服务压力</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>新增快充</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>新增慢充</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>成本_万</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>触发原因</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>低增长(10%)</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C2" t="n">
-        <v>2</v>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>南市街道</t>
-        </is>
-      </c>
-      <c r="E2" t="n">
-        <v>0.9617</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.1331</v>
-      </c>
-      <c r="G2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>6</v>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>基准增长(15%)</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>南市街道</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>0.9117</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.1454</v>
-      </c>
-      <c r="G3" t="n">
-        <v>3</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>18</v>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>基准增长(15%)</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C4" t="n">
-        <v>6</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>新城街道</t>
-        </is>
-      </c>
-      <c r="E4" t="n">
-        <v>0.8595</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.1633</v>
-      </c>
-      <c r="G4" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>6</v>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>2027</v>
-      </c>
-      <c r="C5" t="n">
-        <v>2</v>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>南市街道</t>
-        </is>
-      </c>
-      <c r="E5" t="n">
-        <v>0.9549</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.132</v>
-      </c>
-      <c r="G5" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>6</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>宝塔山街道</t>
-        </is>
-      </c>
-      <c r="E6" t="n">
-        <v>0.9199000000000001</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.1554</v>
-      </c>
-      <c r="G6" t="n">
-        <v>2</v>
-      </c>
-      <c r="H6" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" t="n">
-        <v>12</v>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C7" t="n">
-        <v>2</v>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>南市街道</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>0.8565</v>
-      </c>
-      <c r="F7" t="n">
-        <v>0.1572</v>
-      </c>
-      <c r="G7" t="n">
-        <v>5</v>
-      </c>
-      <c r="H7" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" t="n">
-        <v>30</v>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3</v>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>凤凰山街道</t>
-        </is>
-      </c>
-      <c r="E8" t="n">
-        <v>0.9195</v>
-      </c>
-      <c r="F8" t="n">
-        <v>0.1831</v>
-      </c>
-      <c r="G8" t="n">
-        <v>2</v>
-      </c>
-      <c r="H8" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" t="n">
-        <v>12</v>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>高增长(20%)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>2028</v>
-      </c>
-      <c r="C9" t="n">
-        <v>6</v>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>新城街道</t>
-        </is>
-      </c>
-      <c r="E9" t="n">
-        <v>0.8773</v>
-      </c>
-      <c r="F9" t="n">
-        <v>0.1778</v>
-      </c>
-      <c r="G9" t="n">
-        <v>3</v>
-      </c>
-      <c r="H9" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" t="n">
-        <v>18</v>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>过载分流</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/q4_output/动态扩容方案.xlsx
+++ b/results/q4_output/动态扩容方案.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,214 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:J5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>情景</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>年份</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>区域</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>区域名称</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>健康度</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>服务压力</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>新增快充</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>新增慢充</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>成本_万</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>触发原因</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C2" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>凤凰山街道</t>
+        </is>
+      </c>
+      <c r="E2" t="n">
+        <v>0.8487</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.2306</v>
+      </c>
+      <c r="G2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="n">
+        <v>0</v>
+      </c>
+      <c r="I2" t="n">
+        <v>6</v>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>过载分流</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C3" t="n">
+        <v>4</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>枣园街道</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>0.8548</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.1833</v>
+      </c>
+      <c r="G3" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="n">
+        <v>0</v>
+      </c>
+      <c r="I3" t="n">
+        <v>6</v>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>过载分流</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C4" t="n">
+        <v>3</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>凤凰山街道</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>0.8189</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.2511</v>
+      </c>
+      <c r="G4" t="n">
+        <v>3</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>18</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>过载分流</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C5" t="n">
+        <v>4</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>枣园街道</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.8241000000000001</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1996</v>
+      </c>
+      <c r="G5" t="n">
+        <v>3</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>18</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>过载分流</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/results/q4_output/动态扩容方案.xlsx
+++ b/results/q4_output/动态扩容方案.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -483,152 +483,836 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C2" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>0.8487</v>
+        <v>0.6679</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2306</v>
+        <v>0.0804</v>
       </c>
       <c r="G2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I2" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>过载分流</t>
+          <t>DP优化</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>基准增长(15%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>2028</v>
+        <v>2026</v>
       </c>
       <c r="C3" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>枣园街道</t>
+          <t>真武洞街道（安塞）</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>0.8548</v>
+        <v>0.6219</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1833</v>
+        <v>0.1021</v>
       </c>
       <c r="G3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I3" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>过载分流</t>
+          <t>DP优化</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>高增长(20%)</t>
+          <t>低增长(10%)</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>2028</v>
+        <v>2027</v>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>凤凰山街道</t>
+          <t>姚店镇（经开区）</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>0.8189</v>
+        <v>0.6585</v>
       </c>
       <c r="F4" t="n">
-        <v>0.2511</v>
+        <v>0.0872</v>
       </c>
       <c r="G4" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="I4" t="n">
-        <v>18</v>
+        <v>4</v>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>过载分流</t>
+          <t>DP优化</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>低增长(10%)</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C5" t="n">
+        <v>10</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>真武洞街道（安塞）</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>0.614</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.1107</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>5</v>
+      </c>
+      <c r="I5" t="n">
+        <v>4</v>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>低增长(10%)</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>万花山镇</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>0.892</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.4076</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>5</v>
+      </c>
+      <c r="I6" t="n">
+        <v>4</v>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>低增长(10%)</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C7" t="n">
+        <v>10</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>真武洞街道（安塞）</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.1199</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>5</v>
+      </c>
+      <c r="I7" t="n">
+        <v>4</v>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>姚店镇（经开区）</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" t="n">
+        <v>5</v>
+      </c>
+      <c r="I8" t="n">
+        <v>4</v>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C9" t="n">
+        <v>10</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>真武洞街道（安塞）</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" t="n">
+        <v>5</v>
+      </c>
+      <c r="I9" t="n">
+        <v>4</v>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C10" t="n">
+        <v>9</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>万花山镇</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>0.9133</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>5</v>
+      </c>
+      <c r="I10" t="n">
+        <v>4</v>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C11" t="n">
+        <v>10</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>真武洞街道（安塞）</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>0.6851</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1157</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" t="n">
+        <v>5</v>
+      </c>
+      <c r="I11" t="n">
+        <v>4</v>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>宝塔山街道</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>0.9239000000000001</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1354</v>
+      </c>
+      <c r="G12" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" t="n">
+        <v>5</v>
+      </c>
+      <c r="I12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C13" t="n">
+        <v>9</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>万花山镇</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>0.8269</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.4339</v>
+      </c>
+      <c r="G13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" t="n">
+        <v>5</v>
+      </c>
+      <c r="I13" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>基准增长(15%)</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C14" t="n">
+        <v>10</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>真武洞街道（安塞）</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>0.7053</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1311</v>
+      </c>
+      <c r="G14" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" t="n">
+        <v>5</v>
+      </c>
+      <c r="I14" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
           <t>高增长(20%)</t>
         </is>
       </c>
-      <c r="B5" t="n">
+      <c r="B15" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C15" t="n">
+        <v>8</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>姚店镇（经开区）</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>0.6679</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.0804</v>
+      </c>
+      <c r="G15" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" t="n">
+        <v>5</v>
+      </c>
+      <c r="I15" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>2026</v>
+      </c>
+      <c r="C16" t="n">
+        <v>10</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>真武洞街道（安塞）</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>0.6219</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.1021</v>
+      </c>
+      <c r="G16" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" t="n">
+        <v>5</v>
+      </c>
+      <c r="I16" t="n">
+        <v>4</v>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C17" t="n">
+        <v>9</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>万花山镇</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>0.895</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>5</v>
+      </c>
+      <c r="I17" t="n">
+        <v>4</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>2027</v>
+      </c>
+      <c r="C18" t="n">
+        <v>10</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>真武洞街道（安塞）</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>0.7048</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.1207</v>
+      </c>
+      <c r="G18" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" t="n">
+        <v>5</v>
+      </c>
+      <c r="I18" t="n">
+        <v>4</v>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
         <v>2028</v>
       </c>
-      <c r="C5" t="n">
-        <v>4</v>
-      </c>
-      <c r="D5" t="inlineStr">
+      <c r="C19" t="n">
+        <v>1</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>宝塔山街道</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>0.883</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.1475</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" t="n">
+        <v>5</v>
+      </c>
+      <c r="I19" t="n">
+        <v>4</v>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C20" t="n">
+        <v>2</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>南市街道</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0.9171</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.1469</v>
+      </c>
+      <c r="G20" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" t="n">
+        <v>5</v>
+      </c>
+      <c r="I20" t="n">
+        <v>4</v>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C21" t="n">
+        <v>5</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>枣园街道</t>
         </is>
       </c>
-      <c r="E5" t="n">
-        <v>0.8241000000000001</v>
-      </c>
-      <c r="F5" t="n">
-        <v>0.1996</v>
-      </c>
-      <c r="G5" t="n">
-        <v>3</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>18</v>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>过载分流</t>
+      <c r="E21" t="n">
+        <v>0.9026999999999999</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.221</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>5</v>
+      </c>
+      <c r="I21" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C22" t="n">
+        <v>9</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>万花山镇</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>0.784</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.4725</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" t="n">
+        <v>5</v>
+      </c>
+      <c r="I22" t="n">
+        <v>4</v>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>DP优化</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>高增长(20%)</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>2028</v>
+      </c>
+      <c r="C23" t="n">
+        <v>10</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>真武洞街道（安塞）</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>0.6763</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.1427</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" t="n">
+        <v>5</v>
+      </c>
+      <c r="I23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>DP优化</t>
         </is>
       </c>
     </row>
